--- a/Sample_run/1/student/duongnthe186310/TC5/GradeDetail.xlsx
+++ b/Sample_run/1/student/duongnthe186310/TC5/GradeDetail.xlsx
@@ -933,7 +933,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:R11"/>
+  <x:dimension ref="A1:R13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
@@ -1059,7 +1059,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>47084</x:v>
+        <x:v>33686</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1118,7 +1118,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>47084</x:v>
+        <x:v>33686</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1171,7 +1171,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>47084</x:v>
+        <x:v>33686</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1227,7 +1227,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>47084</x:v>
+        <x:v>33686</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1286,7 +1286,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>47084</x:v>
+        <x:v>33686</x:v>
       </x:c>
       <x:c r="R6" s="2" t="s">
         <x:v>46</x:v>
@@ -1342,7 +1342,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>47084</x:v>
+        <x:v>33686</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
         <x:v>56</x:v>
@@ -1395,7 +1395,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>47084</x:v>
+        <x:v>33686</x:v>
       </x:c>
       <x:c r="Q8" s="0">
         <x:v>4000</x:v>
@@ -1454,7 +1454,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>47084</x:v>
+        <x:v>33686</x:v>
       </x:c>
       <x:c r="R9" s="4" t="s">
         <x:v>60</x:v>
@@ -1492,10 +1492,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
         <x:v>44</x:v>
@@ -1507,7 +1507,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>47084</x:v>
+        <x:v>33686</x:v>
       </x:c>
       <x:c r="Q10" s="0">
         <x:v>4000</x:v>
@@ -1548,27 +1548,139 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="L11" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="M11" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P11" s="0">
+        <x:v>33686</x:v>
+      </x:c>
+      <x:c r="Q11" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R11" s="4" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:18">
+      <x:c r="A12" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="M12" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P12" s="0">
+        <x:v>33686</x:v>
+      </x:c>
+      <x:c r="Q12" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R12" s="4" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:18">
+      <x:c r="A13" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="L11" s="0" t="s">
+      <x:c r="L13" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="M11" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N11" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P11" s="0">
+      <x:c r="M13" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N13" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P13" s="0">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="Q11" s="0">
-        <x:v>47084</x:v>
-      </x:c>
-      <x:c r="R11" s="4" t="s">
+      <x:c r="Q13" s="0">
+        <x:v>33686</x:v>
+      </x:c>
+      <x:c r="R13" s="4" t="s">
         <x:v>60</x:v>
       </x:c>
     </x:row>
